--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -7140,7 +7140,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -7140,7 +7140,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -7140,7 +7140,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -7140,7 +7140,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -7140,7 +7140,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -7140,7 +7140,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251002_171859.xlsx
@@ -7140,7 +7140,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
